--- a/data/batches/2026-10/send_list.xlsx
+++ b/data/batches/2026-10/send_list.xlsx
@@ -901,454 +901,454 @@
     <t>Yuni Marpaung</t>
   </si>
   <si>
-    <t>irfan.rahayu502@outlook.com</t>
-  </si>
-  <si>
-    <t>joko.wibowo645@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>eko.pratama215@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.sitompul434@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.syahputra554@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.wijaya618@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.purnomo145@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>utami.tanjung518@outlook.com</t>
-  </si>
-  <si>
-    <t>fitri.hakim996@outlook.com</t>
-  </si>
-  <si>
-    <t>nur.simanjuntak774@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.halim624@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.saputra848@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.sitompul49@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.saputra313@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.com</t>
-  </si>
-  <si>
-    <t>oki.daeng364@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.nasution839@gmail.com</t>
-  </si>
-  <si>
-    <t>citra.purnomo44@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.lestari977@gmial.com</t>
-  </si>
-  <si>
-    <t>wulan.wijaya969@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.halim495@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.firmansyah990.old@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.pratama248@outlook.com</t>
-  </si>
-  <si>
-    <t>budi.syahputra811@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.wijaya532@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.halim470@outlook.com</t>
-  </si>
-  <si>
-    <t>wahyu.halim598@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.daeng499@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.lestari850@yahoo.co.id; sari.santoso755@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hendra.harahap128@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wahyu.firmansyah515@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wahyu.permana384@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.nugroho728@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.susanto502@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.ramadhan955@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.pane811@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.hakim610@outlook.com</t>
-  </si>
-  <si>
-    <t>agus.nasution246@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.kusuma675@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.harahap261@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.gunawan243@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.purnomo929@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung193@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.harahap839@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>sari.marpaung480@gmail.com</t>
-  </si>
-  <si>
-    <t>tika.daeng308@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.harahap213@outlook.com</t>
-  </si>
-  <si>
-    <t>joko.utomo213@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.sitompul57@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.hakim696@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.marpaung547@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.hidayat159@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.pane31@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak295@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hendra.syahputra501@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.com</t>
-  </si>
-  <si>
-    <t>fajar.kusuma491@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.santoso222@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.rahayu944@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.nasution210@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>yoga.setiawan838@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.sitompul359@gmail.com</t>
-  </si>
-  <si>
-    <t>hendra.sitompul513@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>andi.kusuma335@outlook.com</t>
-  </si>
-  <si>
-    <t>yoga.sitompul246@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.sitompul744@outlook.com</t>
-  </si>
-  <si>
-    <t>gita.halim195@outlook.com</t>
-  </si>
-  <si>
-    <t>lestari.syahputra32@gmail.com</t>
-  </si>
-  <si>
-    <t>surya.santoso508@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.ramadhan727@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.pratama1@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.pane475@outlook.com</t>
-  </si>
-  <si>
-    <t>laras.rahayu46@outlook.com</t>
-  </si>
-  <si>
-    <t>mega.pratama628@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.nugroho155@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.santoso626@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hendra.tanjung449@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.daeng993@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.wijaya214@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.lestari652@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.nasution302@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.wijaya589@gmail.com</t>
-  </si>
-  <si>
-    <t>oki.tanjung474@outlook.com</t>
-  </si>
-  <si>
-    <t>taufik.halim405@outlook.com</t>
-  </si>
-  <si>
-    <t>fitri.halim480@outlook.com</t>
-  </si>
-  <si>
-    <t>lestari.hakim142@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.marpaung269@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.siregar965@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>agus.santoso985@gmail.com</t>
-  </si>
-  <si>
-    <t>rina.harahap48@gmail.com</t>
-  </si>
-  <si>
-    <t>oki.simanjuntak674@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.nasution130@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.santoso755@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>andi.hakim536@outlook.com</t>
-  </si>
-  <si>
-    <t>eko.tanjung306@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.wijaya805@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.setiawan802@outlook.com</t>
-  </si>
-  <si>
-    <t>yuni.susanto823@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.harahap730@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.daeng107@gmail.com</t>
-  </si>
-  <si>
-    <t>indah.saputra104@gmail.com</t>
-  </si>
-  <si>
-    <t>surya.setiawan771@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.harahap695@gmail.com</t>
-  </si>
-  <si>
-    <t>taufik.lestari125@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.wijaya50@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.halim187@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.rahayu752@outlook.com</t>
-  </si>
-  <si>
-    <t>gita.harahap701@outlook.com</t>
-  </si>
-  <si>
-    <t>dimas.ramadhan647@gmail.com</t>
-  </si>
-  <si>
-    <t>hendra.susanto347@outlook.com</t>
-  </si>
-  <si>
-    <t>fajar.daeng98@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>bayu.hakim22@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.pane682@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.susanto481@gmail.com</t>
-  </si>
-  <si>
-    <t>rina.utomo103@gmail.com</t>
-  </si>
-  <si>
-    <t>andi.harahap186@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hendra.saputra659@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.nasution570@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.harahap781@gmail.com</t>
-  </si>
-  <si>
-    <t>budi.harahap271@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>utami.tanjung420@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.nugroho622@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>taufik.hakim575@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>zaki.lestari814@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.nugroho92@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.hidayat760@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.saputra331@gmail.com</t>
-  </si>
-  <si>
-    <t>citra.setiawan654@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.hakim660@gmail.com</t>
-  </si>
-  <si>
-    <t>maya.syahputra695@gmail.com</t>
-  </si>
-  <si>
-    <t>hendra.santoso262@outlook.com</t>
-  </si>
-  <si>
-    <t>irfan.permana862@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>yuni.syahputra865@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.halim677@gmail.com</t>
-  </si>
-  <si>
-    <t>surya.hidayat910@gmail.com</t>
-  </si>
-  <si>
-    <t>maya.pratama207@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.nasution952@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hana.sitompul456@outlook.com</t>
-  </si>
-  <si>
-    <t>budi.tanjung979@outlook.com</t>
-  </si>
-  <si>
-    <t>agus.hidayat505@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.pratama125@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>hana.utomo103@outlook.com</t>
-  </si>
-  <si>
-    <t>kartika.pratama872@gmail.com</t>
-  </si>
-  <si>
-    <t>tika.hidayat507@outlook.com</t>
-  </si>
-  <si>
-    <t>tika.wijaya764@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.marpaung475@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>andi.rahayu333@yahoo.co.id</t>
+    <t>irfan.rahayu502@outlook.example</t>
+  </si>
+  <si>
+    <t>joko.wibowo645@yahoo.example</t>
+  </si>
+  <si>
+    <t>eko.pratama215@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.sitompul434@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.syahputra554@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.wijaya618@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.purnomo145@yahoo.example</t>
+  </si>
+  <si>
+    <t>utami.tanjung518@outlook.example</t>
+  </si>
+  <si>
+    <t>fitri.hakim996@outlook.example</t>
+  </si>
+  <si>
+    <t>nur.simanjuntak774@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.halim624@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.saputra848@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.sitompul49@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.saputra313@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.rahayu13@outlook.example</t>
+  </si>
+  <si>
+    <t>oki.daeng364@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.nasution839@gmail.example</t>
+  </si>
+  <si>
+    <t>citra.purnomo44@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.lestari977@gmial.example</t>
+  </si>
+  <si>
+    <t>wulan.wijaya969@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.halim495@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.firmansyah990.old@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.pratama248@outlook.example</t>
+  </si>
+  <si>
+    <t>budi.syahputra811@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.wijaya532@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.halim470@outlook.example</t>
+  </si>
+  <si>
+    <t>wahyu.halim598@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.daeng499@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.lestari850@yahoo.example; sari.santoso755@yahoo.example</t>
+  </si>
+  <si>
+    <t>hendra.harahap128@yahoo.example</t>
+  </si>
+  <si>
+    <t>wahyu.firmansyah515@yahoo.example</t>
+  </si>
+  <si>
+    <t>wahyu.permana384@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.nugroho728@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.susanto502@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.ramadhan955@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.pane811@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.hakim610@outlook.example</t>
+  </si>
+  <si>
+    <t>agus.nasution246@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.kusuma675@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.harahap261@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.gunawan243@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.purnomo929@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.marpaung193@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.harahap839@yahoo.example</t>
+  </si>
+  <si>
+    <t>sari.marpaung480@gmail.example</t>
+  </si>
+  <si>
+    <t>tika.daeng308@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.harahap213@outlook.example</t>
+  </si>
+  <si>
+    <t>joko.utomo213@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.sitompul57@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.hakim696@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.marpaung547@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.hidayat159@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.pane31@yahoo.example</t>
+  </si>
+  <si>
+    <t>dewi.simanjuntak295@yahoo.example</t>
+  </si>
+  <si>
+    <t>hendra.syahputra501@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.simanjuntak858@gmail.example</t>
+  </si>
+  <si>
+    <t>fajar.kusuma491@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.nasution814@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.santoso222@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.rahayu944@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.nasution210@yahoo.example</t>
+  </si>
+  <si>
+    <t>yoga.setiawan838@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.sitompul359@gmail.example</t>
+  </si>
+  <si>
+    <t>hendra.sitompul513@yahoo.example</t>
+  </si>
+  <si>
+    <t>andi.kusuma335@outlook.example</t>
+  </si>
+  <si>
+    <t>yoga.sitompul246@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.sitompul744@outlook.example</t>
+  </si>
+  <si>
+    <t>gita.halim195@outlook.example</t>
+  </si>
+  <si>
+    <t>lestari.syahputra32@gmail.example</t>
+  </si>
+  <si>
+    <t>surya.santoso508@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.syahputra515@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.ramadhan727@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.pratama1@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.pane475@outlook.example</t>
+  </si>
+  <si>
+    <t>laras.rahayu46@outlook.example</t>
+  </si>
+  <si>
+    <t>mega.pratama628@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.nugroho155@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.santoso626@yahoo.example</t>
+  </si>
+  <si>
+    <t>hendra.tanjung449@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.daeng993@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.wijaya214@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.lestari652@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.nasution302@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.wijaya589@gmail.example</t>
+  </si>
+  <si>
+    <t>oki.tanjung474@outlook.example</t>
+  </si>
+  <si>
+    <t>taufik.halim405@outlook.example</t>
+  </si>
+  <si>
+    <t>fitri.halim480@outlook.example</t>
+  </si>
+  <si>
+    <t>lestari.hakim142@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.marpaung269@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.siregar965@yahoo.example</t>
+  </si>
+  <si>
+    <t>agus.santoso985@gmail.example</t>
+  </si>
+  <si>
+    <t>rina.harahap48@gmail.example</t>
+  </si>
+  <si>
+    <t>oki.simanjuntak674@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.nasution130@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.santoso755@yahoo.example</t>
+  </si>
+  <si>
+    <t>andi.hakim536@outlook.example</t>
+  </si>
+  <si>
+    <t>eko.tanjung306@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.wijaya805@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.setiawan802@outlook.example</t>
+  </si>
+  <si>
+    <t>yuni.susanto823@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.harahap730@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.daeng107@gmail.example</t>
+  </si>
+  <si>
+    <t>indah.saputra104@gmail.example</t>
+  </si>
+  <si>
+    <t>surya.setiawan771@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.harahap695@gmail.example</t>
+  </si>
+  <si>
+    <t>taufik.lestari125@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.wijaya50@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.halim187@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.rahayu752@outlook.example</t>
+  </si>
+  <si>
+    <t>gita.harahap701@outlook.example</t>
+  </si>
+  <si>
+    <t>dimas.ramadhan647@gmail.example</t>
+  </si>
+  <si>
+    <t>hendra.susanto347@outlook.example</t>
+  </si>
+  <si>
+    <t>fajar.daeng98@yahoo.example</t>
+  </si>
+  <si>
+    <t>bayu.hakim22@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.pane682@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.susanto481@gmail.example</t>
+  </si>
+  <si>
+    <t>rina.utomo103@gmail.example</t>
+  </si>
+  <si>
+    <t>andi.harahap186@yahoo.example</t>
+  </si>
+  <si>
+    <t>hendra.saputra659@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.nasution570@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.harahap781@gmail.example</t>
+  </si>
+  <si>
+    <t>budi.harahap271@yahoo.example</t>
+  </si>
+  <si>
+    <t>utami.tanjung420@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.nugroho622@yahoo.example</t>
+  </si>
+  <si>
+    <t>taufik.hakim575@yahoo.example</t>
+  </si>
+  <si>
+    <t>zaki.lestari814@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.nugroho92@yahoo.example</t>
+  </si>
+  <si>
+    <t>wahyu.tanjung859@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.hidayat760@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.saputra331@gmail.example</t>
+  </si>
+  <si>
+    <t>citra.setiawan654@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.hakim660@gmail.example</t>
+  </si>
+  <si>
+    <t>maya.syahputra695@gmail.example</t>
+  </si>
+  <si>
+    <t>hendra.santoso262@outlook.example</t>
+  </si>
+  <si>
+    <t>irfan.permana862@yahoo.example</t>
+  </si>
+  <si>
+    <t>yuni.syahputra865@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.halim677@gmail.example</t>
+  </si>
+  <si>
+    <t>surya.hidayat910@gmail.example</t>
+  </si>
+  <si>
+    <t>maya.pratama207@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.nasution952@yahoo.example</t>
+  </si>
+  <si>
+    <t>hana.sitompul456@outlook.example</t>
+  </si>
+  <si>
+    <t>budi.tanjung979@outlook.example</t>
+  </si>
+  <si>
+    <t>agus.hidayat505@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.pratama125@yahoo.example</t>
+  </si>
+  <si>
+    <t>hana.utomo103@outlook.example</t>
+  </si>
+  <si>
+    <t>kartika.pratama872@gmail.example</t>
+  </si>
+  <si>
+    <t>tika.hidayat507@outlook.example</t>
+  </si>
+  <si>
+    <t>tika.wijaya764@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.marpaung475@yahoo.example</t>
+  </si>
+  <si>
+    <t>andi.rahayu333@yahoo.example</t>
   </si>
   <si>
     <t>JKT</t>
@@ -1378,7 +1378,7 @@
     <t>BENEFIT_PAYMENT</t>
   </si>
   <si>
-    <t>bdg.staff@gmail.com</t>
+    <t>bdg.staff@gmail.example</t>
   </si>
 </sst>
 </file>

--- a/data/batches/2026-10/send_list.xlsx
+++ b/data/batches/2026-10/send_list.xlsx
@@ -40,1345 +40,1345 @@
     <t>2026-10</t>
   </si>
   <si>
-    <t>7797392740</t>
-  </si>
-  <si>
-    <t>7749256988</t>
-  </si>
-  <si>
-    <t>7732613144</t>
-  </si>
-  <si>
-    <t>7746601976</t>
-  </si>
-  <si>
-    <t>7739692553</t>
-  </si>
-  <si>
-    <t>7783449229</t>
-  </si>
-  <si>
-    <t>7702789053</t>
-  </si>
-  <si>
-    <t>7782249451</t>
-  </si>
-  <si>
-    <t>7779284663</t>
-  </si>
-  <si>
-    <t>7729302014</t>
-  </si>
-  <si>
-    <t>7742966156</t>
-  </si>
-  <si>
-    <t>7753347707</t>
-  </si>
-  <si>
-    <t>7714441705</t>
-  </si>
-  <si>
-    <t>7745642201</t>
-  </si>
-  <si>
-    <t>7786367442</t>
-  </si>
-  <si>
-    <t>7769466803</t>
-  </si>
-  <si>
-    <t>7793364709</t>
-  </si>
-  <si>
-    <t>7748329335</t>
-  </si>
-  <si>
-    <t>7783839028</t>
-  </si>
-  <si>
-    <t>7763546687</t>
-  </si>
-  <si>
-    <t>7733237227</t>
-  </si>
-  <si>
-    <t>7785989243</t>
-  </si>
-  <si>
-    <t>7765922652</t>
-  </si>
-  <si>
-    <t>7771186741</t>
-  </si>
-  <si>
-    <t>7776687553</t>
-  </si>
-  <si>
-    <t>7766536090</t>
-  </si>
-  <si>
-    <t>7751757077</t>
-  </si>
-  <si>
-    <t>7778615126</t>
-  </si>
-  <si>
-    <t>7736781978</t>
-  </si>
-  <si>
-    <t>7775301560</t>
-  </si>
-  <si>
-    <t>7761657188</t>
-  </si>
-  <si>
-    <t>7763280819</t>
-  </si>
-  <si>
-    <t>7753065351</t>
-  </si>
-  <si>
-    <t>7797275110</t>
-  </si>
-  <si>
-    <t>7742557333</t>
-  </si>
-  <si>
-    <t>7754227136</t>
-  </si>
-  <si>
-    <t>7772507811</t>
-  </si>
-  <si>
-    <t>7705693153</t>
-  </si>
-  <si>
-    <t>7756158900</t>
-  </si>
-  <si>
-    <t>7743929657</t>
-  </si>
-  <si>
-    <t>7792198416</t>
-  </si>
-  <si>
-    <t>7760743774</t>
-  </si>
-  <si>
-    <t>7755885086</t>
-  </si>
-  <si>
-    <t>7730286979</t>
-  </si>
-  <si>
-    <t>7769179737</t>
-  </si>
-  <si>
-    <t>7712713307</t>
+    <t>7718894612</t>
+  </si>
+  <si>
+    <t>7731296980</t>
+  </si>
+  <si>
+    <t>7758916240</t>
+  </si>
+  <si>
+    <t>7767815376</t>
+  </si>
+  <si>
+    <t>7763222588</t>
+  </si>
+  <si>
+    <t>7714822836</t>
+  </si>
+  <si>
+    <t>7707283943</t>
+  </si>
+  <si>
+    <t>7700459657</t>
+  </si>
+  <si>
+    <t>7721106070</t>
+  </si>
+  <si>
+    <t>7742338752</t>
+  </si>
+  <si>
+    <t>7718573402</t>
+  </si>
+  <si>
+    <t>7731811289</t>
+  </si>
+  <si>
+    <t>7791220776</t>
+  </si>
+  <si>
+    <t>7747431601</t>
+  </si>
+  <si>
+    <t>7771082356</t>
+  </si>
+  <si>
+    <t>7750484006</t>
+  </si>
+  <si>
+    <t>7785536568</t>
+  </si>
+  <si>
+    <t>7788179575</t>
+  </si>
+  <si>
+    <t>7797216942</t>
+  </si>
+  <si>
+    <t>7718917928</t>
+  </si>
+  <si>
+    <t>7728558112</t>
+  </si>
+  <si>
+    <t>7797362304</t>
+  </si>
+  <si>
+    <t>7787614790</t>
+  </si>
+  <si>
+    <t>7707782831</t>
+  </si>
+  <si>
+    <t>7725233449</t>
+  </si>
+  <si>
+    <t>7750592607</t>
+  </si>
+  <si>
+    <t>7751100009</t>
+  </si>
+  <si>
+    <t>7769333424</t>
+  </si>
+  <si>
+    <t>7702412812</t>
+  </si>
+  <si>
+    <t>7761678333</t>
+  </si>
+  <si>
+    <t>7769102383</t>
+  </si>
+  <si>
+    <t>7753786134</t>
+  </si>
+  <si>
+    <t>7772013307</t>
+  </si>
+  <si>
+    <t>7706030061</t>
+  </si>
+  <si>
+    <t>7777262234</t>
+  </si>
+  <si>
+    <t>7789049622</t>
+  </si>
+  <si>
+    <t>7771635505</t>
+  </si>
+  <si>
+    <t>7762813823</t>
+  </si>
+  <si>
+    <t>7722463353</t>
+  </si>
+  <si>
+    <t>7755941962</t>
+  </si>
+  <si>
+    <t>7739722112</t>
+  </si>
+  <si>
+    <t>7718866768</t>
+  </si>
+  <si>
+    <t>7714745595</t>
+  </si>
+  <si>
+    <t>7708859061</t>
+  </si>
+  <si>
+    <t>7756405267</t>
+  </si>
+  <si>
+    <t>7784776864</t>
+  </si>
+  <si>
+    <t>7708477974</t>
+  </si>
+  <si>
+    <t>7776302066</t>
+  </si>
+  <si>
+    <t>7776524680</t>
+  </si>
+  <si>
+    <t>7763560188</t>
+  </si>
+  <si>
+    <t>7750965395</t>
+  </si>
+  <si>
+    <t>7716699365</t>
+  </si>
+  <si>
+    <t>7705715932</t>
+  </si>
+  <si>
+    <t>7714564412</t>
+  </si>
+  <si>
+    <t>7725189553</t>
+  </si>
+  <si>
+    <t>7721631253</t>
+  </si>
+  <si>
+    <t>7732525224</t>
+  </si>
+  <si>
+    <t>7746972013</t>
+  </si>
+  <si>
+    <t>7706162073</t>
+  </si>
+  <si>
+    <t>7797082955</t>
+  </si>
+  <si>
+    <t>7740319965</t>
+  </si>
+  <si>
+    <t>7755247355</t>
+  </si>
+  <si>
+    <t>7735240906</t>
+  </si>
+  <si>
+    <t>7721891437</t>
+  </si>
+  <si>
+    <t>7721226939</t>
+  </si>
+  <si>
+    <t>7700846238</t>
+  </si>
+  <si>
+    <t>7709655248</t>
+  </si>
+  <si>
+    <t>7708537307</t>
+  </si>
+  <si>
+    <t>7792600411</t>
+  </si>
+  <si>
+    <t>7770336774</t>
+  </si>
+  <si>
+    <t>7735509484</t>
+  </si>
+  <si>
+    <t>7779501978</t>
+  </si>
+  <si>
+    <t>7793154748</t>
+  </si>
+  <si>
+    <t>7717874442</t>
+  </si>
+  <si>
+    <t>7724397078</t>
+  </si>
+  <si>
+    <t>7731384310</t>
+  </si>
+  <si>
+    <t>7784819264</t>
+  </si>
+  <si>
+    <t>7787118590</t>
+  </si>
+  <si>
+    <t>7775513957</t>
+  </si>
+  <si>
+    <t>7769597089</t>
+  </si>
+  <si>
+    <t>7771906617</t>
+  </si>
+  <si>
+    <t>7772659592</t>
+  </si>
+  <si>
+    <t>7751182973</t>
+  </si>
+  <si>
+    <t>7756602216</t>
+  </si>
+  <si>
+    <t>7734210904</t>
+  </si>
+  <si>
+    <t>7732561133</t>
+  </si>
+  <si>
+    <t>7794547417</t>
+  </si>
+  <si>
+    <t>7758967630</t>
+  </si>
+  <si>
+    <t>7703607897</t>
+  </si>
+  <si>
+    <t>7726098760</t>
+  </si>
+  <si>
+    <t>7726333635</t>
+  </si>
+  <si>
+    <t>7722623610</t>
+  </si>
+  <si>
+    <t>7770077703</t>
+  </si>
+  <si>
+    <t>7790542559</t>
   </si>
   <si>
     <t>7762946999</t>
   </si>
   <si>
-    <t>7718730552</t>
-  </si>
-  <si>
-    <t>7767647122</t>
-  </si>
-  <si>
-    <t>7767887787</t>
-  </si>
-  <si>
-    <t>7753264999</t>
-  </si>
-  <si>
-    <t>7709863395</t>
-  </si>
-  <si>
-    <t>7777245482</t>
-  </si>
-  <si>
-    <t>7729011601</t>
-  </si>
-  <si>
-    <t>7706601187</t>
-  </si>
-  <si>
-    <t>7707449684</t>
-  </si>
-  <si>
-    <t>7763751773</t>
-  </si>
-  <si>
-    <t>7748432235</t>
-  </si>
-  <si>
-    <t>7766744724</t>
-  </si>
-  <si>
-    <t>7717799490</t>
-  </si>
-  <si>
-    <t>7762109156</t>
-  </si>
-  <si>
-    <t>7707975643</t>
-  </si>
-  <si>
-    <t>7792660933</t>
-  </si>
-  <si>
-    <t>7729293288</t>
-  </si>
-  <si>
-    <t>7720178198</t>
-  </si>
-  <si>
-    <t>7712316065</t>
-  </si>
-  <si>
-    <t>7721151267</t>
-  </si>
-  <si>
-    <t>7763804169</t>
-  </si>
-  <si>
-    <t>7725441977</t>
-  </si>
-  <si>
-    <t>7719988999</t>
-  </si>
-  <si>
-    <t>7798227701</t>
-  </si>
-  <si>
-    <t>7791034485</t>
-  </si>
-  <si>
-    <t>7771098395</t>
-  </si>
-  <si>
-    <t>7726252489</t>
-  </si>
-  <si>
-    <t>7741716988</t>
-  </si>
-  <si>
-    <t>7788089448</t>
-  </si>
-  <si>
-    <t>7782617476</t>
-  </si>
-  <si>
-    <t>7713492973</t>
-  </si>
-  <si>
-    <t>7772659592</t>
-  </si>
-  <si>
-    <t>7716816202</t>
-  </si>
-  <si>
-    <t>7798909779</t>
-  </si>
-  <si>
-    <t>7712913856</t>
-  </si>
-  <si>
-    <t>7734030825</t>
-  </si>
-  <si>
-    <t>7767498935</t>
-  </si>
-  <si>
-    <t>7705060240</t>
-  </si>
-  <si>
-    <t>7750174190</t>
-  </si>
-  <si>
-    <t>7772762267</t>
-  </si>
-  <si>
-    <t>7735596930</t>
-  </si>
-  <si>
-    <t>7719786335</t>
-  </si>
-  <si>
-    <t>7751668571</t>
-  </si>
-  <si>
-    <t>7724564659</t>
-  </si>
-  <si>
-    <t>7727221816</t>
-  </si>
-  <si>
-    <t>7755849998</t>
-  </si>
-  <si>
-    <t>7714902427</t>
-  </si>
-  <si>
-    <t>7757844933</t>
-  </si>
-  <si>
-    <t>7752861743</t>
-  </si>
-  <si>
-    <t>7710321322</t>
-  </si>
-  <si>
-    <t>7730757251</t>
-  </si>
-  <si>
-    <t>7774895425</t>
-  </si>
-  <si>
-    <t>7751741412</t>
-  </si>
-  <si>
-    <t>7736540850</t>
-  </si>
-  <si>
-    <t>7701243361</t>
-  </si>
-  <si>
-    <t>7745671728</t>
-  </si>
-  <si>
-    <t>7724617701</t>
-  </si>
-  <si>
-    <t>7786944595</t>
-  </si>
-  <si>
-    <t>7778835366</t>
-  </si>
-  <si>
-    <t>7745707321</t>
-  </si>
-  <si>
-    <t>7779657394</t>
-  </si>
-  <si>
-    <t>7756144614</t>
-  </si>
-  <si>
-    <t>7731387065</t>
-  </si>
-  <si>
-    <t>7755975969</t>
-  </si>
-  <si>
-    <t>7705005731</t>
-  </si>
-  <si>
-    <t>7767001985</t>
-  </si>
-  <si>
-    <t>7705343718</t>
-  </si>
-  <si>
-    <t>7760649836</t>
-  </si>
-  <si>
-    <t>7705210085</t>
-  </si>
-  <si>
-    <t>7785506317</t>
-  </si>
-  <si>
-    <t>7762339422</t>
-  </si>
-  <si>
-    <t>7759692397</t>
-  </si>
-  <si>
-    <t>7786916157</t>
-  </si>
-  <si>
-    <t>7713064856</t>
-  </si>
-  <si>
-    <t>7765840877</t>
-  </si>
-  <si>
-    <t>7773308448</t>
-  </si>
-  <si>
-    <t>7753976479</t>
-  </si>
-  <si>
-    <t>7721060695</t>
-  </si>
-  <si>
-    <t>7768362661</t>
-  </si>
-  <si>
-    <t>7747882670</t>
-  </si>
-  <si>
-    <t>7797690923</t>
-  </si>
-  <si>
-    <t>7705041543</t>
-  </si>
-  <si>
-    <t>7711884273</t>
-  </si>
-  <si>
-    <t>7797569860</t>
-  </si>
-  <si>
-    <t>7764327521</t>
-  </si>
-  <si>
-    <t>7719229864</t>
-  </si>
-  <si>
-    <t>7700233103</t>
-  </si>
-  <si>
-    <t>7789676464</t>
-  </si>
-  <si>
-    <t>7709453430</t>
-  </si>
-  <si>
-    <t>7796525371</t>
-  </si>
-  <si>
-    <t>7735443603</t>
-  </si>
-  <si>
-    <t>7701865699</t>
-  </si>
-  <si>
-    <t>7774802330</t>
-  </si>
-  <si>
-    <t>7701319280</t>
-  </si>
-  <si>
-    <t>7722424939</t>
-  </si>
-  <si>
-    <t>7716186351</t>
-  </si>
-  <si>
-    <t>7740435562</t>
-  </si>
-  <si>
-    <t>7790348591</t>
-  </si>
-  <si>
-    <t>7741441600</t>
-  </si>
-  <si>
-    <t>7789730017</t>
-  </si>
-  <si>
-    <t>7732110252</t>
-  </si>
-  <si>
-    <t>7707237990</t>
-  </si>
-  <si>
-    <t>7751079192</t>
-  </si>
-  <si>
-    <t>Irfan Rahayu</t>
-  </si>
-  <si>
-    <t>Joko Wibowo</t>
-  </si>
-  <si>
-    <t>Eko Pratama</t>
-  </si>
-  <si>
-    <t>Hana Sitompul</t>
-  </si>
-  <si>
-    <t>Joko Syahputra</t>
-  </si>
-  <si>
-    <t>Gita Wijaya</t>
-  </si>
-  <si>
-    <t>Fitri Purnomo</t>
-  </si>
-  <si>
-    <t>Utami Tanjung</t>
-  </si>
-  <si>
-    <t>Fitri Hakim</t>
-  </si>
-  <si>
-    <t>Nur Simanjuntak</t>
-  </si>
-  <si>
-    <t>Bayu Halim</t>
-  </si>
-  <si>
-    <t>Dimas Saputra</t>
-  </si>
-  <si>
-    <t>Lestari Sitompul</t>
-  </si>
-  <si>
-    <t>Joko Saputra</t>
-  </si>
-  <si>
-    <t>Fitri Rahayu</t>
-  </si>
-  <si>
-    <t>Oki Daeng</t>
-  </si>
-  <si>
-    <t>Nur Nasution</t>
-  </si>
-  <si>
-    <t>Citra Purnomo</t>
-  </si>
-  <si>
-    <t>Utami Lestari</t>
-  </si>
-  <si>
-    <t>Wulan Wijaya</t>
-  </si>
-  <si>
-    <t>Putri Halim</t>
-  </si>
-  <si>
-    <t>Yuni Firmansyah</t>
-  </si>
-  <si>
-    <t>Irfan Pratama</t>
-  </si>
-  <si>
-    <t>Budi Syahputra</t>
-  </si>
-  <si>
-    <t>Eko Wijaya</t>
-  </si>
-  <si>
-    <t>Yoga Halim</t>
-  </si>
-  <si>
-    <t>Wahyu Halim</t>
-  </si>
-  <si>
-    <t>Sari Daeng</t>
-  </si>
-  <si>
-    <t>Wulan Lestari</t>
-  </si>
-  <si>
-    <t>Hendra Harahap</t>
-  </si>
-  <si>
-    <t>Wahyu Firmansyah</t>
-  </si>
-  <si>
-    <t>Wahyu Permana</t>
-  </si>
-  <si>
-    <t>Yuni Nugroho</t>
-  </si>
-  <si>
-    <t>Bayu Susanto</t>
-  </si>
-  <si>
-    <t>Eko Ramadhan</t>
-  </si>
-  <si>
-    <t>Dimas Pane</t>
-  </si>
-  <si>
-    <t>Rahmat Hakim</t>
-  </si>
-  <si>
-    <t>Agus Nasution</t>
-  </si>
-  <si>
-    <t>Rahmat Kusuma</t>
-  </si>
-  <si>
-    <t>Fitri Harahap</t>
-  </si>
-  <si>
-    <t>Rahmat Gunawan</t>
-  </si>
-  <si>
-    <t>Wahyu Purnomo</t>
-  </si>
-  <si>
-    <t>Wahyu Marpaung</t>
-  </si>
-  <si>
-    <t>Lestari Harahap</t>
-  </si>
-  <si>
-    <t>Sari Marpaung</t>
-  </si>
-  <si>
-    <t>Tika Daeng</t>
-  </si>
-  <si>
-    <t>Agus Harahap</t>
-  </si>
-  <si>
-    <t>Joko Utomo</t>
-  </si>
-  <si>
-    <t>Putri Sitompul</t>
-  </si>
-  <si>
-    <t>Bayu Hakim</t>
-  </si>
-  <si>
-    <t>Wulan Marpaung</t>
-  </si>
-  <si>
-    <t>Agus Hidayat</t>
-  </si>
-  <si>
-    <t>Yoga Pane</t>
-  </si>
-  <si>
-    <t>Dewi Simanjuntak</t>
-  </si>
-  <si>
-    <t>Hendra Syahputra</t>
-  </si>
-  <si>
-    <t>Fajar Kusuma</t>
-  </si>
-  <si>
-    <t>Sari Nasution</t>
-  </si>
-  <si>
-    <t>Rizky Santoso</t>
-  </si>
-  <si>
-    <t>Andi Rahayu</t>
-  </si>
-  <si>
-    <t>Zaki Nasution</t>
-  </si>
-  <si>
-    <t>Yoga Setiawan</t>
-  </si>
-  <si>
-    <t>Andi Sitompul</t>
-  </si>
-  <si>
-    <t>Hendra Sitompul</t>
-  </si>
-  <si>
-    <t>Andi Kusuma</t>
-  </si>
-  <si>
-    <t>Yoga Sitompul</t>
-  </si>
-  <si>
-    <t>Mega Sitompul</t>
-  </si>
-  <si>
-    <t>Gita Halim</t>
-  </si>
-  <si>
-    <t>Lestari Syahputra</t>
-  </si>
-  <si>
-    <t>Surya Santoso</t>
-  </si>
-  <si>
-    <t>Mega Syahputra</t>
-  </si>
-  <si>
-    <t>Agus Ramadhan</t>
-  </si>
-  <si>
-    <t>Gita Pratama</t>
-  </si>
-  <si>
-    <t>Laras Rahayu</t>
-  </si>
-  <si>
-    <t>Mega Pratama</t>
-  </si>
-  <si>
-    <t>Putri Nugroho</t>
-  </si>
-  <si>
-    <t>Fitri Santoso</t>
-  </si>
-  <si>
-    <t>Hendra Tanjung</t>
-  </si>
-  <si>
-    <t>Irfan Daeng</t>
-  </si>
-  <si>
-    <t>Bayu Wijaya</t>
-  </si>
-  <si>
-    <t>Rahmat Lestari</t>
-  </si>
-  <si>
-    <t>Yoga Nasution</t>
-  </si>
-  <si>
-    <t>Oki Tanjung</t>
-  </si>
-  <si>
-    <t>Taufik Halim</t>
-  </si>
-  <si>
-    <t>Fitri Halim</t>
-  </si>
-  <si>
-    <t>Lestari Hakim</t>
-  </si>
-  <si>
-    <t>Mega Marpaung</t>
-  </si>
-  <si>
-    <t>Utami Siregar</t>
-  </si>
-  <si>
-    <t>Agus Santoso</t>
-  </si>
-  <si>
-    <t>Rina Harahap</t>
-  </si>
-  <si>
-    <t>Oki Simanjuntak</t>
-  </si>
-  <si>
-    <t>Wulan Nasution</t>
-  </si>
-  <si>
-    <t>Sari Santoso</t>
-  </si>
-  <si>
-    <t>Andi Hakim</t>
-  </si>
-  <si>
-    <t>Eko Tanjung</t>
-  </si>
-  <si>
-    <t>Rahmat Wijaya</t>
-  </si>
-  <si>
-    <t>Yuni Setiawan</t>
-  </si>
-  <si>
-    <t>Yuni Susanto</t>
-  </si>
-  <si>
-    <t>Lestari Daeng</t>
-  </si>
-  <si>
-    <t>Indah Saputra</t>
-  </si>
-  <si>
-    <t>Surya Setiawan</t>
-  </si>
-  <si>
-    <t>Vina Harahap</t>
-  </si>
-  <si>
-    <t>Taufik Lestari</t>
-  </si>
-  <si>
-    <t>Yoga Wijaya</t>
-  </si>
-  <si>
-    <t>Gilang Rahayu</t>
-  </si>
-  <si>
-    <t>Gita Harahap</t>
-  </si>
-  <si>
-    <t>Dimas Ramadhan</t>
-  </si>
-  <si>
-    <t>Hendra Susanto</t>
-  </si>
-  <si>
-    <t>Fajar Daeng</t>
-  </si>
-  <si>
-    <t>Gita Pane</t>
-  </si>
-  <si>
-    <t>Eko Susanto</t>
-  </si>
-  <si>
-    <t>Rina Utomo</t>
-  </si>
-  <si>
-    <t>Andi Harahap</t>
-  </si>
-  <si>
-    <t>Hendra Saputra</t>
-  </si>
-  <si>
-    <t>Bayu Nasution</t>
-  </si>
-  <si>
-    <t>Wulan Harahap</t>
-  </si>
-  <si>
-    <t>Budi Harahap</t>
-  </si>
-  <si>
-    <t>Rizky Nugroho</t>
-  </si>
-  <si>
-    <t>Taufik Hakim</t>
-  </si>
-  <si>
-    <t>Zaki Lestari</t>
-  </si>
-  <si>
-    <t>Irfan Nugroho</t>
-  </si>
-  <si>
-    <t>Wahyu Tanjung</t>
-  </si>
-  <si>
-    <t>Yuni Hidayat</t>
-  </si>
-  <si>
-    <t>Utami Saputra</t>
-  </si>
-  <si>
-    <t>Citra Setiawan</t>
-  </si>
-  <si>
-    <t>Maya Syahputra</t>
-  </si>
-  <si>
-    <t>Hendra Santoso</t>
-  </si>
-  <si>
-    <t>Irfan Permana</t>
-  </si>
-  <si>
-    <t>Yuni Syahputra</t>
-  </si>
-  <si>
-    <t>Surya Hidayat</t>
-  </si>
-  <si>
-    <t>Maya Pratama</t>
-  </si>
-  <si>
-    <t>Budi Tanjung</t>
-  </si>
-  <si>
-    <t>Bayu Pratama</t>
-  </si>
-  <si>
-    <t>Hana Utomo</t>
-  </si>
-  <si>
-    <t>Kartika Pratama</t>
-  </si>
-  <si>
-    <t>Tika Hidayat</t>
-  </si>
-  <si>
-    <t>Tika Wijaya</t>
-  </si>
-  <si>
-    <t>Yuni Marpaung</t>
-  </si>
-  <si>
-    <t>irfan.rahayu502@outlook.example</t>
-  </si>
-  <si>
-    <t>joko.wibowo645@yahoo.example</t>
-  </si>
-  <si>
-    <t>eko.pratama215@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.sitompul434@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.syahputra554@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.wijaya618@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.purnomo145@yahoo.example</t>
-  </si>
-  <si>
-    <t>utami.tanjung518@outlook.example</t>
-  </si>
-  <si>
-    <t>fitri.hakim996@outlook.example</t>
-  </si>
-  <si>
-    <t>nur.simanjuntak774@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.halim624@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.saputra848@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.sitompul49@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.saputra313@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.example</t>
-  </si>
-  <si>
-    <t>oki.daeng364@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.nasution839@gmail.example</t>
-  </si>
-  <si>
-    <t>citra.purnomo44@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.lestari977@gmial.example</t>
-  </si>
-  <si>
-    <t>wulan.wijaya969@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.halim495@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.firmansyah990.old@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.pratama248@outlook.example</t>
-  </si>
-  <si>
-    <t>budi.syahputra811@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.wijaya532@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.halim470@outlook.example</t>
-  </si>
-  <si>
-    <t>wahyu.halim598@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.daeng499@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.lestari850@yahoo.example; sari.santoso755@yahoo.example</t>
-  </si>
-  <si>
-    <t>hendra.harahap128@yahoo.example</t>
-  </si>
-  <si>
-    <t>wahyu.firmansyah515@yahoo.example</t>
-  </si>
-  <si>
-    <t>wahyu.permana384@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.nugroho728@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.susanto502@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.ramadhan955@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.pane811@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.hakim610@outlook.example</t>
-  </si>
-  <si>
-    <t>agus.nasution246@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.kusuma675@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.harahap261@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.gunawan243@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.purnomo929@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung193@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.harahap839@yahoo.example</t>
-  </si>
-  <si>
-    <t>sari.marpaung480@gmail.example</t>
-  </si>
-  <si>
-    <t>tika.daeng308@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.harahap213@outlook.example</t>
-  </si>
-  <si>
-    <t>joko.utomo213@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.sitompul57@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.hakim696@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.marpaung547@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.hidayat159@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.pane31@yahoo.example</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak295@yahoo.example</t>
-  </si>
-  <si>
-    <t>hendra.syahputra501@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.example</t>
-  </si>
-  <si>
-    <t>fajar.kusuma491@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.santoso222@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.rahayu944@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.nasution210@yahoo.example</t>
-  </si>
-  <si>
-    <t>yoga.setiawan838@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.sitompul359@gmail.example</t>
-  </si>
-  <si>
-    <t>hendra.sitompul513@yahoo.example</t>
-  </si>
-  <si>
-    <t>andi.kusuma335@outlook.example</t>
-  </si>
-  <si>
-    <t>yoga.sitompul246@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.sitompul744@outlook.example</t>
-  </si>
-  <si>
-    <t>gita.halim195@outlook.example</t>
-  </si>
-  <si>
-    <t>lestari.syahputra32@gmail.example</t>
-  </si>
-  <si>
-    <t>surya.santoso508@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.ramadhan727@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.pratama1@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.pane475@outlook.example</t>
-  </si>
-  <si>
-    <t>laras.rahayu46@outlook.example</t>
-  </si>
-  <si>
-    <t>mega.pratama628@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.nugroho155@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.santoso626@yahoo.example</t>
-  </si>
-  <si>
-    <t>hendra.tanjung449@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.daeng993@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.wijaya214@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.lestari652@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.nasution302@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.wijaya589@gmail.example</t>
-  </si>
-  <si>
-    <t>oki.tanjung474@outlook.example</t>
-  </si>
-  <si>
-    <t>taufik.halim405@outlook.example</t>
-  </si>
-  <si>
-    <t>fitri.halim480@outlook.example</t>
-  </si>
-  <si>
-    <t>lestari.hakim142@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.marpaung269@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.siregar965@yahoo.example</t>
-  </si>
-  <si>
-    <t>agus.santoso985@gmail.example</t>
-  </si>
-  <si>
-    <t>rina.harahap48@gmail.example</t>
-  </si>
-  <si>
-    <t>oki.simanjuntak674@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.nasution130@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.santoso755@yahoo.example</t>
-  </si>
-  <si>
-    <t>andi.hakim536@outlook.example</t>
-  </si>
-  <si>
-    <t>eko.tanjung306@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.wijaya805@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.setiawan802@outlook.example</t>
-  </si>
-  <si>
-    <t>yuni.susanto823@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.harahap730@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.daeng107@gmail.example</t>
-  </si>
-  <si>
-    <t>indah.saputra104@gmail.example</t>
-  </si>
-  <si>
-    <t>surya.setiawan771@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.harahap695@gmail.example</t>
-  </si>
-  <si>
-    <t>taufik.lestari125@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.wijaya50@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.halim187@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.rahayu752@outlook.example</t>
-  </si>
-  <si>
-    <t>gita.harahap701@outlook.example</t>
-  </si>
-  <si>
-    <t>dimas.ramadhan647@gmail.example</t>
-  </si>
-  <si>
-    <t>hendra.susanto347@outlook.example</t>
-  </si>
-  <si>
-    <t>fajar.daeng98@yahoo.example</t>
-  </si>
-  <si>
-    <t>bayu.hakim22@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.pane682@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.susanto481@gmail.example</t>
-  </si>
-  <si>
-    <t>rina.utomo103@gmail.example</t>
-  </si>
-  <si>
-    <t>andi.harahap186@yahoo.example</t>
-  </si>
-  <si>
-    <t>hendra.saputra659@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.nasution570@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.harahap781@gmail.example</t>
-  </si>
-  <si>
-    <t>budi.harahap271@yahoo.example</t>
-  </si>
-  <si>
-    <t>utami.tanjung420@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.nugroho622@yahoo.example</t>
-  </si>
-  <si>
-    <t>taufik.hakim575@yahoo.example</t>
-  </si>
-  <si>
-    <t>zaki.lestari814@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.nugroho92@yahoo.example</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.hidayat760@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.saputra331@gmail.example</t>
-  </si>
-  <si>
-    <t>citra.setiawan654@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.hakim660@gmail.example</t>
-  </si>
-  <si>
-    <t>maya.syahputra695@gmail.example</t>
-  </si>
-  <si>
-    <t>hendra.santoso262@outlook.example</t>
-  </si>
-  <si>
-    <t>irfan.permana862@yahoo.example</t>
-  </si>
-  <si>
-    <t>yuni.syahputra865@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.halim677@gmail.example</t>
-  </si>
-  <si>
-    <t>surya.hidayat910@gmail.example</t>
-  </si>
-  <si>
-    <t>maya.pratama207@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.nasution952@yahoo.example</t>
-  </si>
-  <si>
-    <t>hana.sitompul456@outlook.example</t>
-  </si>
-  <si>
-    <t>budi.tanjung979@outlook.example</t>
-  </si>
-  <si>
-    <t>agus.hidayat505@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.pratama125@yahoo.example</t>
-  </si>
-  <si>
-    <t>hana.utomo103@outlook.example</t>
-  </si>
-  <si>
-    <t>kartika.pratama872@gmail.example</t>
-  </si>
-  <si>
-    <t>tika.hidayat507@outlook.example</t>
-  </si>
-  <si>
-    <t>tika.wijaya764@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.marpaung475@yahoo.example</t>
-  </si>
-  <si>
-    <t>andi.rahayu333@yahoo.example</t>
+    <t>7737128405</t>
+  </si>
+  <si>
+    <t>7790534939</t>
+  </si>
+  <si>
+    <t>7775387892</t>
+  </si>
+  <si>
+    <t>7765801256</t>
+  </si>
+  <si>
+    <t>7727198217</t>
+  </si>
+  <si>
+    <t>7759130138</t>
+  </si>
+  <si>
+    <t>7730366744</t>
+  </si>
+  <si>
+    <t>7709444919</t>
+  </si>
+  <si>
+    <t>7718399272</t>
+  </si>
+  <si>
+    <t>7722802311</t>
+  </si>
+  <si>
+    <t>7739030668</t>
+  </si>
+  <si>
+    <t>7783946312</t>
+  </si>
+  <si>
+    <t>7731801879</t>
+  </si>
+  <si>
+    <t>7763307350</t>
+  </si>
+  <si>
+    <t>7788831949</t>
+  </si>
+  <si>
+    <t>7713292035</t>
+  </si>
+  <si>
+    <t>7788259980</t>
+  </si>
+  <si>
+    <t>7723663627</t>
+  </si>
+  <si>
+    <t>7701003907</t>
+  </si>
+  <si>
+    <t>7761373242</t>
+  </si>
+  <si>
+    <t>7731273768</t>
+  </si>
+  <si>
+    <t>7746988465</t>
+  </si>
+  <si>
+    <t>7760300517</t>
+  </si>
+  <si>
+    <t>7706429168</t>
+  </si>
+  <si>
+    <t>7723838471</t>
+  </si>
+  <si>
+    <t>7772994394</t>
+  </si>
+  <si>
+    <t>7769004609</t>
+  </si>
+  <si>
+    <t>7798497241</t>
+  </si>
+  <si>
+    <t>7718289020</t>
+  </si>
+  <si>
+    <t>7714277469</t>
+  </si>
+  <si>
+    <t>7763472851</t>
+  </si>
+  <si>
+    <t>7778645999</t>
+  </si>
+  <si>
+    <t>7718428697</t>
+  </si>
+  <si>
+    <t>7703899080</t>
+  </si>
+  <si>
+    <t>7708722439</t>
+  </si>
+  <si>
+    <t>7702768399</t>
+  </si>
+  <si>
+    <t>7739161898</t>
+  </si>
+  <si>
+    <t>7718627072</t>
+  </si>
+  <si>
+    <t>7779700726</t>
+  </si>
+  <si>
+    <t>7728750039</t>
+  </si>
+  <si>
+    <t>7758558155</t>
+  </si>
+  <si>
+    <t>7748349156</t>
+  </si>
+  <si>
+    <t>7754913568</t>
+  </si>
+  <si>
+    <t>7730016121</t>
+  </si>
+  <si>
+    <t>7782088000</t>
+  </si>
+  <si>
+    <t>7776698447</t>
+  </si>
+  <si>
+    <t>7725425138</t>
+  </si>
+  <si>
+    <t>7735146367</t>
+  </si>
+  <si>
+    <t>7799119294</t>
+  </si>
+  <si>
+    <t>7707927644</t>
+  </si>
+  <si>
+    <t>7703852550</t>
+  </si>
+  <si>
+    <t>7716650857</t>
+  </si>
+  <si>
+    <t>7744656587</t>
+  </si>
+  <si>
+    <t>7756826099</t>
+  </si>
+  <si>
+    <t>7735199926</t>
+  </si>
+  <si>
+    <t>Hendra P******</t>
+  </si>
+  <si>
+    <t>Rahmat S**********</t>
+  </si>
+  <si>
+    <t>Surya W*****</t>
+  </si>
+  <si>
+    <t>Utami K*****</t>
+  </si>
+  <si>
+    <t>Gita T******</t>
+  </si>
+  <si>
+    <t>Maya D****</t>
+  </si>
+  <si>
+    <t>Gita L******</t>
+  </si>
+  <si>
+    <t>Mega S********</t>
+  </si>
+  <si>
+    <t>Citra H****</t>
+  </si>
+  <si>
+    <t>Andi D****</t>
+  </si>
+  <si>
+    <t>Tika G******</t>
+  </si>
+  <si>
+    <t>Laras M*******</t>
+  </si>
+  <si>
+    <t>Joko S******</t>
+  </si>
+  <si>
+    <t>Rina M*******</t>
+  </si>
+  <si>
+    <t>Yuni S**********</t>
+  </si>
+  <si>
+    <t>Nur T******</t>
+  </si>
+  <si>
+    <t>Lestari S*******</t>
+  </si>
+  <si>
+    <t>Irfan S*******</t>
+  </si>
+  <si>
+    <t>Bayu S*******</t>
+  </si>
+  <si>
+    <t>Fitri T******</t>
+  </si>
+  <si>
+    <t>Indah P******</t>
+  </si>
+  <si>
+    <t>Dimas P***</t>
+  </si>
+  <si>
+    <t>Fajar H******</t>
+  </si>
+  <si>
+    <t>Joko W*****</t>
+  </si>
+  <si>
+    <t>Nanda U****</t>
+  </si>
+  <si>
+    <t>Gita S******</t>
+  </si>
+  <si>
+    <t>Hana S******</t>
+  </si>
+  <si>
+    <t>Sari M*******</t>
+  </si>
+  <si>
+    <t>Fajar H****</t>
+  </si>
+  <si>
+    <t>Lestari G******</t>
+  </si>
+  <si>
+    <t>Maya R*****</t>
+  </si>
+  <si>
+    <t>Oki R*****</t>
+  </si>
+  <si>
+    <t>Joko P******</t>
+  </si>
+  <si>
+    <t>Andi S******</t>
+  </si>
+  <si>
+    <t>Bayu M*******</t>
+  </si>
+  <si>
+    <t>Taufik T******</t>
+  </si>
+  <si>
+    <t>Taufik P******</t>
+  </si>
+  <si>
+    <t>Rina S******</t>
+  </si>
+  <si>
+    <t>Kartika P******</t>
+  </si>
+  <si>
+    <t>Kartika L******</t>
+  </si>
+  <si>
+    <t>Gilang S*******</t>
+  </si>
+  <si>
+    <t>Joko H******</t>
+  </si>
+  <si>
+    <t>Kartika R*******</t>
+  </si>
+  <si>
+    <t>Putri H****</t>
+  </si>
+  <si>
+    <t>Andi R*****</t>
+  </si>
+  <si>
+    <t>Oki S*******</t>
+  </si>
+  <si>
+    <t>Yuni P******</t>
+  </si>
+  <si>
+    <t>Eko S**********</t>
+  </si>
+  <si>
+    <t>Bayu N******</t>
+  </si>
+  <si>
+    <t>Tika S*******</t>
+  </si>
+  <si>
+    <t>Irfan H******</t>
+  </si>
+  <si>
+    <t>Yuni U****</t>
+  </si>
+  <si>
+    <t>Hendra S******</t>
+  </si>
+  <si>
+    <t>Yoga P******</t>
+  </si>
+  <si>
+    <t>Rina U****</t>
+  </si>
+  <si>
+    <t>Vina H******</t>
+  </si>
+  <si>
+    <t>Budi S******</t>
+  </si>
+  <si>
+    <t>Andi N******</t>
+  </si>
+  <si>
+    <t>Dimas U****</t>
+  </si>
+  <si>
+    <t>Gilang S********</t>
+  </si>
+  <si>
+    <t>Bayu P******</t>
+  </si>
+  <si>
+    <t>Yuni H****</t>
+  </si>
+  <si>
+    <t>Vina L******</t>
+  </si>
+  <si>
+    <t>Nur S********</t>
+  </si>
+  <si>
+    <t>Bayu S******</t>
+  </si>
+  <si>
+    <t>Yoga N*******</t>
+  </si>
+  <si>
+    <t>Putri M*******</t>
+  </si>
+  <si>
+    <t>Nanda N******</t>
+  </si>
+  <si>
+    <t>Mega K*****</t>
+  </si>
+  <si>
+    <t>Joko S*******</t>
+  </si>
+  <si>
+    <t>Budi R*******</t>
+  </si>
+  <si>
+    <t>Eko N******</t>
+  </si>
+  <si>
+    <t>Nanda P***</t>
+  </si>
+  <si>
+    <t>Fitri P******</t>
+  </si>
+  <si>
+    <t>Bayu R*****</t>
+  </si>
+  <si>
+    <t>Nanda M*******</t>
+  </si>
+  <si>
+    <t>Yuni S*******</t>
+  </si>
+  <si>
+    <t>Hendra T******</t>
+  </si>
+  <si>
+    <t>Hendra S********</t>
+  </si>
+  <si>
+    <t>Rina N******</t>
+  </si>
+  <si>
+    <t>Utami P******</t>
+  </si>
+  <si>
+    <t>Nur S*******</t>
+  </si>
+  <si>
+    <t>Putri U****</t>
+  </si>
+  <si>
+    <t>Wulan S******</t>
+  </si>
+  <si>
+    <t>Kartika H****</t>
+  </si>
+  <si>
+    <t>Fitri U****</t>
+  </si>
+  <si>
+    <t>Yoga M*******</t>
+  </si>
+  <si>
+    <t>Maya S*******</t>
+  </si>
+  <si>
+    <t>Wulan S**********</t>
+  </si>
+  <si>
+    <t>Agus H******</t>
+  </si>
+  <si>
+    <t>Citra P******</t>
+  </si>
+  <si>
+    <t>Eko D****</t>
+  </si>
+  <si>
+    <t>Zaki S*******</t>
+  </si>
+  <si>
+    <t>Fajar L******</t>
+  </si>
+  <si>
+    <t>Mega P******</t>
+  </si>
+  <si>
+    <t>Sari U****</t>
+  </si>
+  <si>
+    <t>Rina W*****</t>
+  </si>
+  <si>
+    <t>Eko S********</t>
+  </si>
+  <si>
+    <t>Fajar S**********</t>
+  </si>
+  <si>
+    <t>Laras T******</t>
+  </si>
+  <si>
+    <t>Irfan N*******</t>
+  </si>
+  <si>
+    <t>Irfan S********</t>
+  </si>
+  <si>
+    <t>Nur G******</t>
+  </si>
+  <si>
+    <t>Indah W*****</t>
+  </si>
+  <si>
+    <t>Indah R*****</t>
+  </si>
+  <si>
+    <t>Yoga S*******</t>
+  </si>
+  <si>
+    <t>Putri P******</t>
+  </si>
+  <si>
+    <t>Wahyu U****</t>
+  </si>
+  <si>
+    <t>Fajar S********</t>
+  </si>
+  <si>
+    <t>Bayu H******</t>
+  </si>
+  <si>
+    <t>Putri W*****</t>
+  </si>
+  <si>
+    <t>Joko H****</t>
+  </si>
+  <si>
+    <t>Oki K*****</t>
+  </si>
+  <si>
+    <t>Sari S******</t>
+  </si>
+  <si>
+    <t>Oki P***</t>
+  </si>
+  <si>
+    <t>Yuni N******</t>
+  </si>
+  <si>
+    <t>Joko N*******</t>
+  </si>
+  <si>
+    <t>Wulan W*****</t>
+  </si>
+  <si>
+    <t>Yuni P***</t>
+  </si>
+  <si>
+    <t>Dimas D****</t>
+  </si>
+  <si>
+    <t>Oki H******</t>
+  </si>
+  <si>
+    <t>Dewi S******</t>
+  </si>
+  <si>
+    <t>Wulan P******</t>
+  </si>
+  <si>
+    <t>Wahyu P***</t>
+  </si>
+  <si>
+    <t>Vina S********</t>
+  </si>
+  <si>
+    <t>Wahyu H****</t>
+  </si>
+  <si>
+    <t>Taufik N******</t>
+  </si>
+  <si>
+    <t>Zaki W*****</t>
+  </si>
+  <si>
+    <t>Dimas H******</t>
+  </si>
+  <si>
+    <t>Indah M*******</t>
+  </si>
+  <si>
+    <t>Putri N*******</t>
+  </si>
+  <si>
+    <t>Dewi P******</t>
+  </si>
+  <si>
+    <t>Nur N******</t>
+  </si>
+  <si>
+    <t>Joko U****</t>
+  </si>
+  <si>
+    <t>Hana H******</t>
+  </si>
+  <si>
+    <t>Nur S******</t>
+  </si>
+  <si>
+    <t>Indah F*********</t>
+  </si>
+  <si>
+    <t>customer.0284@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0687@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0322@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0665@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0402@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0651@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0624@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0089@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0111@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0373@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0613@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0238@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0277@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0595@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0003@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0287@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0639@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0275@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0869@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0127@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0833@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0298@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0447@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0417@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0368@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0031@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0492@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0792@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0401@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0561@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0200@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0305@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0838@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0466@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0230@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0250@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0251@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0043@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0563@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0343@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0577@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0677@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0593@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0533@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0778@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0726@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0465@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0201@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0736@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0046@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0036@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0015@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0738@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0263@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0511@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0619@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0294@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0246@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0058@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0633@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0809@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0133@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0060@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0631@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0028@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0112@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0540@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0498@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0448@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0049@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0243@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0710@gmial.example</t>
+  </si>
+  <si>
+    <t>customer.0073@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0714@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0554@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0652@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0167@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0729@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0435@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0222@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0021@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0488@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0763@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0434@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0483@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0509@gmail.example; customer.0355@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0325@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0180@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0208@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0009@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0013@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0100@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0033@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0025@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0735@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0693@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0057@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0016@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0542@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0586@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0576@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0346@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0783@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0621@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0470@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0292@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0874@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0781@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0801@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0443@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0396@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0353@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0575@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0756@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0834@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0602@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0138@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0795@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0183@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0018@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0426@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0453@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0413@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0476@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0571@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0831@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0360@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0084@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0390@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0767@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0503@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0784@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0186.old@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0896@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0314@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0830@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0204@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0568@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0141@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0450@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0174@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0108@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0101@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0898.old@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0236@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0213@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0419@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0654@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0262@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0212@gmail.example</t>
+  </si>
+  <si>
+    <t>YGY</t>
+  </si>
+  <si>
+    <t>MKS</t>
+  </si>
+  <si>
+    <t>MDN</t>
+  </si>
+  <si>
+    <t>BDG</t>
+  </si>
+  <si>
+    <t>SBY</t>
   </si>
   <si>
     <t>JKT</t>
   </si>
   <si>
-    <t>YGY</t>
-  </si>
-  <si>
-    <t>MDN</t>
-  </si>
-  <si>
-    <t>SBY</t>
-  </si>
-  <si>
-    <t>MKS</t>
-  </si>
-  <si>
-    <t>BDG</t>
+    <t>REINSTATEMENT</t>
+  </si>
+  <si>
+    <t>BENEFIT_PAYMENT</t>
   </si>
   <si>
     <t>MATURITY</t>
   </si>
   <si>
-    <t>REINSTATEMENT</t>
-  </si>
-  <si>
-    <t>BENEFIT_PAYMENT</t>
-  </si>
-  <si>
-    <t>bdg.staff@gmail.example</t>
+    <t>ygy.staff@gmail.example</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1793,7 @@
         <v>445</v>
       </c>
       <c r="F4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1810,7 +1810,7 @@
         <v>298</v>
       </c>
       <c r="E5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F5" t="s">
         <v>451</v>
@@ -1830,10 +1830,10 @@
         <v>299</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1870,7 +1870,7 @@
         <v>301</v>
       </c>
       <c r="E8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F8" t="s">
         <v>453</v>
@@ -1890,10 +1890,10 @@
         <v>302</v>
       </c>
       <c r="E9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1910,10 +1910,10 @@
         <v>303</v>
       </c>
       <c r="E10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1930,7 +1930,7 @@
         <v>304</v>
       </c>
       <c r="E11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F11" t="s">
         <v>452</v>
@@ -1950,10 +1950,10 @@
         <v>305</v>
       </c>
       <c r="E12" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1970,10 +1970,10 @@
         <v>306</v>
       </c>
       <c r="E13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1990,10 +1990,10 @@
         <v>307</v>
       </c>
       <c r="E14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>308</v>
       </c>
       <c r="E15" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2030,10 +2030,10 @@
         <v>309</v>
       </c>
       <c r="E16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2050,7 +2050,7 @@
         <v>310</v>
       </c>
       <c r="E17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F17" t="s">
         <v>451</v>
@@ -2070,7 +2070,7 @@
         <v>311</v>
       </c>
       <c r="E18" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F18" t="s">
         <v>453</v>
@@ -2090,7 +2090,7 @@
         <v>312</v>
       </c>
       <c r="E19" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F19" t="s">
         <v>453</v>
@@ -2110,10 +2110,10 @@
         <v>313</v>
       </c>
       <c r="E20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2130,7 +2130,7 @@
         <v>314</v>
       </c>
       <c r="E21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F21" t="s">
         <v>453</v>
@@ -2150,10 +2150,10 @@
         <v>315</v>
       </c>
       <c r="E22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2170,10 +2170,10 @@
         <v>316</v>
       </c>
       <c r="E23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F23" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2190,10 +2190,10 @@
         <v>317</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2210,7 +2210,7 @@
         <v>318</v>
       </c>
       <c r="E25" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F25" t="s">
         <v>451</v>
@@ -2230,10 +2230,10 @@
         <v>319</v>
       </c>
       <c r="E26" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F26" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2250,10 +2250,10 @@
         <v>320</v>
       </c>
       <c r="E27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2270,7 +2270,7 @@
         <v>321</v>
       </c>
       <c r="E28" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F28" t="s">
         <v>453</v>
@@ -2290,10 +2290,10 @@
         <v>322</v>
       </c>
       <c r="E29" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F29" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2310,10 +2310,10 @@
         <v>323</v>
       </c>
       <c r="E30" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F30" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2330,7 +2330,7 @@
         <v>324</v>
       </c>
       <c r="E31" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F31" t="s">
         <v>453</v>
@@ -2350,13 +2350,13 @@
         <v>325</v>
       </c>
       <c r="E32" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F32" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -2370,13 +2370,13 @@
         <v>326</v>
       </c>
       <c r="E33" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F33" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2393,10 +2393,10 @@
         <v>445</v>
       </c>
       <c r="F34" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -2410,13 +2410,13 @@
         <v>328</v>
       </c>
       <c r="E35" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F35" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -2430,13 +2430,13 @@
         <v>329</v>
       </c>
       <c r="E36" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F36" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2450,13 +2450,13 @@
         <v>330</v>
       </c>
       <c r="E37" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F37" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2470,13 +2470,13 @@
         <v>331</v>
       </c>
       <c r="E38" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F38" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -2490,13 +2490,13 @@
         <v>332</v>
       </c>
       <c r="E39" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F39" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2510,13 +2510,13 @@
         <v>333</v>
       </c>
       <c r="E40" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F40" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -2530,13 +2530,13 @@
         <v>334</v>
       </c>
       <c r="E41" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F41" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -2550,13 +2550,13 @@
         <v>335</v>
       </c>
       <c r="E42" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F42" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -2570,13 +2570,13 @@
         <v>336</v>
       </c>
       <c r="E43" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F43" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -2590,16 +2590,13 @@
         <v>337</v>
       </c>
       <c r="E44" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F44" t="s">
-        <v>453</v>
-      </c>
-      <c r="G44" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -2613,13 +2610,13 @@
         <v>338</v>
       </c>
       <c r="E45" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F45" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -2633,13 +2630,13 @@
         <v>339</v>
       </c>
       <c r="E46" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F46" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -2653,13 +2650,13 @@
         <v>340</v>
       </c>
       <c r="E47" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F47" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -2673,13 +2670,13 @@
         <v>341</v>
       </c>
       <c r="E48" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F48" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -2693,13 +2690,13 @@
         <v>342</v>
       </c>
       <c r="E49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F49" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -2713,13 +2710,16 @@
         <v>343</v>
       </c>
       <c r="E50" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F50" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>451</v>
+      </c>
+      <c r="G50" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2733,13 +2733,13 @@
         <v>344</v>
       </c>
       <c r="E51" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F51" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2753,13 +2753,13 @@
         <v>345</v>
       </c>
       <c r="E52" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F52" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2773,13 +2773,13 @@
         <v>346</v>
       </c>
       <c r="E53" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F53" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -2793,13 +2793,13 @@
         <v>347</v>
       </c>
       <c r="E54" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F54" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -2813,13 +2813,13 @@
         <v>348</v>
       </c>
       <c r="E55" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F55" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>7</v>
       </c>
@@ -2833,13 +2833,13 @@
         <v>349</v>
       </c>
       <c r="E56" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F56" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D57" t="s">
         <v>350</v>
@@ -2856,10 +2856,10 @@
         <v>446</v>
       </c>
       <c r="F57" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>7</v>
       </c>
@@ -2867,19 +2867,19 @@
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
         <v>351</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F58" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2893,13 +2893,13 @@
         <v>352</v>
       </c>
       <c r="E59" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F59" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>7</v>
       </c>
@@ -2907,19 +2907,19 @@
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="D60" t="s">
         <v>353</v>
       </c>
       <c r="E60" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F60" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>7</v>
       </c>
@@ -2927,19 +2927,19 @@
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
         <v>354</v>
       </c>
       <c r="E61" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F61" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>7</v>
       </c>
@@ -2947,19 +2947,19 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D62" t="s">
         <v>355</v>
       </c>
       <c r="E62" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F62" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>7</v>
       </c>
@@ -2967,19 +2967,19 @@
         <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D63" t="s">
         <v>356</v>
       </c>
       <c r="E63" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F63" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>7</v>
       </c>
@@ -2987,16 +2987,16 @@
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D64" t="s">
         <v>357</v>
       </c>
       <c r="E64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F64" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3007,16 +3007,16 @@
         <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D65" t="s">
         <v>358</v>
       </c>
       <c r="E65" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F65" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3027,7 +3027,7 @@
         <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
         <v>359</v>
@@ -3047,16 +3047,16 @@
         <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D67" t="s">
         <v>360</v>
       </c>
       <c r="E67" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F67" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3067,13 +3067,13 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D68" t="s">
         <v>361</v>
       </c>
       <c r="E68" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F68" t="s">
         <v>451</v>
@@ -3087,7 +3087,7 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D69" t="s">
         <v>362</v>
@@ -3096,7 +3096,7 @@
         <v>447</v>
       </c>
       <c r="F69" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3107,16 +3107,16 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D70" t="s">
         <v>363</v>
       </c>
       <c r="E70" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F70" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3127,16 +3127,16 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D71" t="s">
         <v>364</v>
       </c>
       <c r="E71" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F71" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3147,13 +3147,13 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D72" t="s">
         <v>365</v>
       </c>
       <c r="E72" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F72" t="s">
         <v>451</v>
@@ -3167,13 +3167,13 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D73" t="s">
         <v>366</v>
       </c>
       <c r="E73" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F73" t="s">
         <v>453</v>
@@ -3187,13 +3187,13 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D74" t="s">
         <v>367</v>
       </c>
       <c r="E74" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F74" t="s">
         <v>451</v>
@@ -3207,13 +3207,13 @@
         <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="D75" t="s">
         <v>368</v>
       </c>
       <c r="E75" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F75" t="s">
         <v>452</v>
@@ -3227,16 +3227,16 @@
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D76" t="s">
         <v>369</v>
       </c>
       <c r="E76" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F76" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3247,16 +3247,16 @@
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D77" t="s">
         <v>370</v>
       </c>
       <c r="E77" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F77" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3267,16 +3267,16 @@
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D78" t="s">
         <v>371</v>
       </c>
       <c r="E78" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F78" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3287,16 +3287,16 @@
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D79" t="s">
         <v>372</v>
       </c>
       <c r="E79" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F79" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3307,16 +3307,16 @@
         <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D80" t="s">
         <v>373</v>
       </c>
       <c r="E80" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F80" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3327,16 +3327,16 @@
         <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D81" t="s">
         <v>374</v>
       </c>
       <c r="E81" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F81" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3347,16 +3347,16 @@
         <v>88</v>
       </c>
       <c r="C82" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D82" t="s">
         <v>375</v>
       </c>
       <c r="E82" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F82" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3367,16 +3367,16 @@
         <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D83" t="s">
         <v>376</v>
       </c>
       <c r="E83" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F83" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3387,13 +3387,13 @@
         <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D84" t="s">
         <v>377</v>
       </c>
       <c r="E84" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F84" t="s">
         <v>451</v>
@@ -3407,16 +3407,16 @@
         <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="D85" t="s">
         <v>378</v>
       </c>
       <c r="E85" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F85" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3427,16 +3427,16 @@
         <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>239</v>
+        <v>170</v>
       </c>
       <c r="D86" t="s">
         <v>379</v>
       </c>
       <c r="E86" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F86" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3447,13 +3447,13 @@
         <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D87" t="s">
         <v>380</v>
       </c>
       <c r="E87" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F87" t="s">
         <v>451</v>
@@ -3467,7 +3467,7 @@
         <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D88" t="s">
         <v>381</v>
@@ -3476,7 +3476,7 @@
         <v>450</v>
       </c>
       <c r="F88" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3487,16 +3487,16 @@
         <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D89" t="s">
         <v>382</v>
       </c>
       <c r="E89" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F89" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3507,16 +3507,16 @@
         <v>96</v>
       </c>
       <c r="C90" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D90" t="s">
         <v>383</v>
       </c>
       <c r="E90" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F90" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3527,16 +3527,16 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D91" t="s">
         <v>384</v>
       </c>
       <c r="E91" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F91" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3547,16 +3547,16 @@
         <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D92" t="s">
         <v>385</v>
       </c>
       <c r="E92" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F92" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3567,13 +3567,13 @@
         <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D93" t="s">
         <v>386</v>
       </c>
       <c r="E93" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F93" t="s">
         <v>451</v>
@@ -3587,7 +3587,7 @@
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D94" t="s">
         <v>387</v>
@@ -3596,7 +3596,7 @@
         <v>445</v>
       </c>
       <c r="F94" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3607,16 +3607,16 @@
         <v>101</v>
       </c>
       <c r="C95" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D95" t="s">
         <v>388</v>
       </c>
       <c r="E95" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F95" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3627,7 +3627,7 @@
         <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D96" t="s">
         <v>389</v>
@@ -3636,7 +3636,7 @@
         <v>450</v>
       </c>
       <c r="F96" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3647,16 +3647,16 @@
         <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="D97" t="s">
         <v>390</v>
       </c>
       <c r="E97" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F97" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3667,16 +3667,16 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D98" t="s">
         <v>391</v>
       </c>
       <c r="E98" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F98" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3687,16 +3687,16 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D99" t="s">
         <v>392</v>
       </c>
       <c r="E99" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F99" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3707,13 +3707,13 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D100" t="s">
         <v>393</v>
       </c>
       <c r="E100" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F100" t="s">
         <v>452</v>
@@ -3727,16 +3727,16 @@
         <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D101" t="s">
         <v>394</v>
       </c>
       <c r="E101" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F101" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3747,7 +3747,7 @@
         <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D102" t="s">
         <v>395</v>
@@ -3756,7 +3756,7 @@
         <v>450</v>
       </c>
       <c r="F102" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3767,16 +3767,16 @@
         <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D103" t="s">
         <v>396</v>
       </c>
       <c r="E103" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F103" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3787,13 +3787,13 @@
         <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D104" t="s">
         <v>397</v>
       </c>
       <c r="E104" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F104" t="s">
         <v>453</v>
@@ -3807,16 +3807,16 @@
         <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D105" t="s">
         <v>398</v>
       </c>
       <c r="E105" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F105" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3827,16 +3827,16 @@
         <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D106" t="s">
         <v>399</v>
       </c>
       <c r="E106" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F106" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3847,13 +3847,13 @@
         <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
         <v>400</v>
       </c>
       <c r="E107" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F107" t="s">
         <v>451</v>
@@ -3867,13 +3867,13 @@
         <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D108" t="s">
         <v>401</v>
       </c>
       <c r="E108" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F108" t="s">
         <v>451</v>
@@ -3887,16 +3887,16 @@
         <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>178</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>402</v>
       </c>
       <c r="E109" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F109" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3907,13 +3907,13 @@
         <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D110" t="s">
         <v>403</v>
       </c>
       <c r="E110" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F110" t="s">
         <v>452</v>
@@ -3927,16 +3927,16 @@
         <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D111" t="s">
         <v>404</v>
       </c>
       <c r="E111" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F111" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3947,16 +3947,16 @@
         <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D112" t="s">
         <v>405</v>
       </c>
       <c r="E112" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F112" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3967,13 +3967,13 @@
         <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>406</v>
       </c>
       <c r="E113" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F113" t="s">
         <v>452</v>
@@ -3987,7 +3987,7 @@
         <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D114" t="s">
         <v>407</v>
@@ -3996,7 +3996,7 @@
         <v>449</v>
       </c>
       <c r="F114" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4007,16 +4007,16 @@
         <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>207</v>
+        <v>264</v>
       </c>
       <c r="D115" t="s">
         <v>408</v>
       </c>
       <c r="E115" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F115" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4027,13 +4027,13 @@
         <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
         <v>409</v>
       </c>
       <c r="E116" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F116" t="s">
         <v>453</v>
@@ -4047,13 +4047,13 @@
         <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="D117" t="s">
         <v>410</v>
       </c>
       <c r="E117" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F117" t="s">
         <v>453</v>
@@ -4067,16 +4067,16 @@
         <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
         <v>411</v>
       </c>
       <c r="E118" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F118" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4087,7 +4087,7 @@
         <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D119" t="s">
         <v>412</v>
@@ -4096,7 +4096,7 @@
         <v>450</v>
       </c>
       <c r="F119" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4107,16 +4107,16 @@
         <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D120" t="s">
         <v>413</v>
       </c>
       <c r="E120" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F120" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4127,16 +4127,16 @@
         <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="D121" t="s">
         <v>414</v>
       </c>
       <c r="E121" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F121" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4147,16 +4147,16 @@
         <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D122" t="s">
         <v>415</v>
       </c>
       <c r="E122" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F122" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4167,13 +4167,13 @@
         <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D123" t="s">
         <v>416</v>
       </c>
       <c r="E123" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F123" t="s">
         <v>452</v>
@@ -4187,13 +4187,13 @@
         <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="D124" t="s">
         <v>417</v>
       </c>
       <c r="E124" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F124" t="s">
         <v>451</v>
@@ -4207,7 +4207,7 @@
         <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D125" t="s">
         <v>418</v>
@@ -4216,7 +4216,7 @@
         <v>446</v>
       </c>
       <c r="F125" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4227,16 +4227,16 @@
         <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D126" t="s">
         <v>419</v>
       </c>
       <c r="E126" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F126" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4247,13 +4247,13 @@
         <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D127" t="s">
         <v>420</v>
       </c>
       <c r="E127" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F127" t="s">
         <v>452</v>
@@ -4267,16 +4267,16 @@
         <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D128" t="s">
         <v>421</v>
       </c>
       <c r="E128" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F128" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4287,13 +4287,13 @@
         <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D129" t="s">
         <v>422</v>
       </c>
       <c r="E129" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F129" t="s">
         <v>452</v>
@@ -4307,13 +4307,13 @@
         <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="D130" t="s">
         <v>423</v>
       </c>
       <c r="E130" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F130" t="s">
         <v>451</v>
@@ -4327,7 +4327,7 @@
         <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D131" t="s">
         <v>424</v>
@@ -4336,7 +4336,7 @@
         <v>446</v>
       </c>
       <c r="F131" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4347,16 +4347,16 @@
         <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D132" t="s">
         <v>425</v>
       </c>
       <c r="E132" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F132" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4367,16 +4367,16 @@
         <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="D133" t="s">
         <v>426</v>
       </c>
       <c r="E133" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F133" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4387,16 +4387,16 @@
         <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D134" t="s">
         <v>427</v>
       </c>
       <c r="E134" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F134" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4407,16 +4407,16 @@
         <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D135" t="s">
         <v>428</v>
       </c>
       <c r="E135" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F135" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4427,16 +4427,16 @@
         <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="D136" t="s">
         <v>429</v>
       </c>
       <c r="E136" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F136" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4447,16 +4447,16 @@
         <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="D137" t="s">
         <v>430</v>
       </c>
       <c r="E137" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F137" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4467,16 +4467,16 @@
         <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D138" t="s">
         <v>431</v>
       </c>
       <c r="E138" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F138" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4487,13 +4487,13 @@
         <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D139" t="s">
         <v>432</v>
       </c>
       <c r="E139" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F139" t="s">
         <v>451</v>
@@ -4507,13 +4507,13 @@
         <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D140" t="s">
         <v>433</v>
       </c>
       <c r="E140" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F140" t="s">
         <v>451</v>
@@ -4527,16 +4527,16 @@
         <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>285</v>
       </c>
       <c r="D141" t="s">
         <v>434</v>
       </c>
       <c r="E141" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F141" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4553,10 +4553,10 @@
         <v>435</v>
       </c>
       <c r="E142" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F142" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4567,16 +4567,16 @@
         <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D143" t="s">
         <v>436</v>
       </c>
       <c r="E143" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F143" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4587,13 +4587,13 @@
         <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D144" t="s">
         <v>437</v>
       </c>
       <c r="E144" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F144" t="s">
         <v>451</v>
@@ -4607,7 +4607,7 @@
         <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D145" t="s">
         <v>438</v>
@@ -4627,13 +4627,13 @@
         <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D146" t="s">
         <v>439</v>
       </c>
       <c r="E146" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F146" t="s">
         <v>453</v>
@@ -4647,16 +4647,16 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D147" t="s">
         <v>440</v>
       </c>
       <c r="E147" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F147" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4667,16 +4667,16 @@
         <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D148" t="s">
         <v>441</v>
       </c>
       <c r="E148" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F148" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4687,16 +4687,16 @@
         <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D149" t="s">
         <v>442</v>
       </c>
       <c r="E149" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F149" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4707,16 +4707,16 @@
         <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D150" t="s">
         <v>443</v>
       </c>
       <c r="E150" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F150" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4727,16 +4727,16 @@
         <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>216</v>
+        <v>294</v>
       </c>
       <c r="D151" t="s">
         <v>444</v>
       </c>
       <c r="E151" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F151" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
